--- a/event_registration_forms/031_stage_play_production_application_form--event_registration_forms.xlsx
+++ b/event_registration_forms/031_stage_play_production_application_form--event_registration_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -671,7 +671,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>production_details_name</t>
+          <t>production_details_name_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>production_details</t>
+          <t>production_details_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Production Details</t>
+          <t>Production Details 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>production_details</t>
+          <t>production_details_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Production Details</t>
+          <t>Production Details 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>actor_details</t>
+          <t>actor_details_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Actor Details</t>
+          <t>Actor Details 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Crew Details Name</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Crew Details Position</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Crew Details Email</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Crew Details Phone</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>production_details</t>
+          <t>production_details_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Production Details</t>
+          <t>Production Details 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes (2)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
